--- a/docs/dashboards/or-monthly-psi/OR_Monthly_PSI_RawData.xlsx
+++ b/docs/dashboards/or-monthly-psi/OR_Monthly_PSI_RawData.xlsx
@@ -22620,7 +22620,7 @@
         <v>213</v>
       </c>
       <c r="G716" s="7" t="n">
-        <v>434</v>
+        <v>492</v>
       </c>
     </row>
     <row r="717">
@@ -22837,7 +22837,7 @@
         <v>597</v>
       </c>
       <c r="G723" s="7" t="n">
-        <v>853</v>
+        <v>892</v>
       </c>
     </row>
     <row r="724">
@@ -23054,7 +23054,7 @@
         <v>548</v>
       </c>
       <c r="G730" s="7" t="n">
-        <v>1114</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="731">
@@ -23240,7 +23240,7 @@
         <v>919</v>
       </c>
       <c r="G736" s="7" t="n">
-        <v>987</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="737">
@@ -23426,7 +23426,7 @@
         <v>886</v>
       </c>
       <c r="G742" s="7" t="n">
-        <v>987</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="743">
@@ -23581,7 +23581,7 @@
         <v>679</v>
       </c>
       <c r="G747" s="7" t="n">
-        <v>1511</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="748">
@@ -26385,7 +26385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G959"/>
+  <dimension ref="A1:G961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -47053,7 +47053,7 @@
       </c>
       <c r="B727" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C727" s="6" t="inlineStr">
@@ -47069,15 +47069,17 @@
       <c r="E727" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F727" s="7" t="n"/>
+      <c r="F727" s="7" t="n">
+        <v>4</v>
+      </c>
       <c r="G727" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B728" s="5" t="inlineStr">
@@ -47087,28 +47089,24 @@
       </c>
       <c r="C728" s="6" t="inlineStr">
         <is>
-          <t>Concealed Set</t>
+          <t>Split AC (Inverter)</t>
         </is>
       </c>
       <c r="D728" s="6" t="inlineStr">
         <is>
-          <t>ABNW60GM3T</t>
-        </is>
-      </c>
-      <c r="E728" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F728" s="7" t="n">
-        <v>4</v>
-      </c>
+          <t>NV182H</t>
+        </is>
+      </c>
+      <c r="E728" s="7" t="n"/>
+      <c r="F728" s="7" t="n"/>
       <c r="G728" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B729" s="5" t="inlineStr">
@@ -47135,7 +47133,7 @@
     <row r="730">
       <c r="A730" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B730" s="5" t="inlineStr">
@@ -47162,7 +47160,7 @@
     <row r="731">
       <c r="A731" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B731" s="5" t="inlineStr">
@@ -47189,7 +47187,7 @@
     <row r="732">
       <c r="A732" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B732" s="5" t="inlineStr">
@@ -47208,20 +47206,22 @@
         </is>
       </c>
       <c r="E732" s="7" t="n"/>
-      <c r="F732" s="7" t="n"/>
+      <c r="F732" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="G732" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B733" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C733" s="6" t="inlineStr">
@@ -47234,12 +47234,12 @@
           <t>NV182H</t>
         </is>
       </c>
-      <c r="E733" s="7" t="n"/>
-      <c r="F733" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E733" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F733" s="7" t="n"/>
       <c r="G733" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="734">
@@ -47250,7 +47250,7 @@
       </c>
       <c r="B734" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C734" s="6" t="inlineStr">
@@ -47268,13 +47268,13 @@
       </c>
       <c r="F734" s="7" t="n"/>
       <c r="G734" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B735" s="5" t="inlineStr">
@@ -47284,26 +47284,24 @@
       </c>
       <c r="C735" s="6" t="inlineStr">
         <is>
-          <t>Split AC (Inverter)</t>
+          <t>Concealed Set</t>
         </is>
       </c>
       <c r="D735" s="6" t="inlineStr">
         <is>
-          <t>NV182H</t>
-        </is>
-      </c>
-      <c r="E735" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ABNQ60GM3T</t>
+        </is>
+      </c>
+      <c r="E735" s="7" t="n"/>
       <c r="F735" s="7" t="n"/>
       <c r="G735" s="7" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B736" s="5" t="inlineStr">
@@ -47322,20 +47320,22 @@
         </is>
       </c>
       <c r="E736" s="7" t="n"/>
-      <c r="F736" s="7" t="n"/>
+      <c r="F736" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G736" s="7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B737" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C737" s="6" t="inlineStr">
@@ -47350,11 +47350,9 @@
       </c>
       <c r="E737" s="7" t="n"/>
       <c r="F737" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G737" s="7" t="n">
-        <v>37</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G737" s="7" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="5" t="inlineStr">
@@ -47364,7 +47362,7 @@
       </c>
       <c r="B738" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C738" s="6" t="inlineStr">
@@ -47379,19 +47377,21 @@
       </c>
       <c r="E738" s="7" t="n"/>
       <c r="F738" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G738" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G738" s="7" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B739" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C739" s="6" t="inlineStr">
@@ -47406,11 +47406,9 @@
       </c>
       <c r="E739" s="7" t="n"/>
       <c r="F739" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G739" s="7" t="n">
-        <v>35</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G739" s="7" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="5" t="inlineStr">
@@ -47420,7 +47418,7 @@
       </c>
       <c r="B740" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C740" s="6" t="inlineStr">
@@ -47434,15 +47432,15 @@
         </is>
       </c>
       <c r="E740" s="7" t="n"/>
-      <c r="F740" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G740" s="7" t="n"/>
+      <c r="F740" s="7" t="n"/>
+      <c r="G740" s="7" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B741" s="5" t="inlineStr">
@@ -47469,12 +47467,12 @@
     <row r="742">
       <c r="A742" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B742" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C742" s="6" t="inlineStr">
@@ -47487,10 +47485,12 @@
           <t>ABNQ60GM3T</t>
         </is>
       </c>
-      <c r="E742" s="7" t="n"/>
+      <c r="E742" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F742" s="7" t="n"/>
       <c r="G742" s="7" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="743">
@@ -47501,7 +47501,7 @@
       </c>
       <c r="B743" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C743" s="6" t="inlineStr">
@@ -47515,12 +47515,12 @@
         </is>
       </c>
       <c r="E743" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F743" s="7" t="n"/>
-      <c r="G743" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="F743" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G743" s="7" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="5" t="inlineStr">
@@ -47530,7 +47530,7 @@
       </c>
       <c r="B744" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C744" s="6" t="inlineStr">
@@ -47544,17 +47544,17 @@
         </is>
       </c>
       <c r="E744" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F744" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G744" s="7" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F744" s="7" t="n"/>
+      <c r="G744" s="7" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B745" s="5" t="inlineStr">
@@ -47569,21 +47569,19 @@
       </c>
       <c r="D745" s="6" t="inlineStr">
         <is>
-          <t>ABNQ60GM3T</t>
-        </is>
-      </c>
-      <c r="E745" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ABNQ34GM3T</t>
+        </is>
+      </c>
+      <c r="E745" s="7" t="n"/>
       <c r="F745" s="7" t="n"/>
       <c r="G745" s="7" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B746" s="5" t="inlineStr">
@@ -47610,7 +47608,7 @@
     <row r="747">
       <c r="A747" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B747" s="5" t="inlineStr">
@@ -47637,7 +47635,7 @@
     <row r="748">
       <c r="A748" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B748" s="5" t="inlineStr">
@@ -47664,7 +47662,7 @@
     <row r="749">
       <c r="A749" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B749" s="5" t="inlineStr">
@@ -47691,12 +47689,12 @@
     <row r="750">
       <c r="A750" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B750" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C750" s="6" t="inlineStr">
@@ -47709,11 +47707,13 @@
           <t>ABNQ34GM3T</t>
         </is>
       </c>
-      <c r="E750" s="7" t="n"/>
-      <c r="F750" s="7" t="n"/>
-      <c r="G750" s="7" t="n">
-        <v>8</v>
-      </c>
+      <c r="E750" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F750" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G750" s="7" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="5" t="inlineStr">
@@ -47723,7 +47723,7 @@
       </c>
       <c r="B751" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C751" s="6" t="inlineStr">
@@ -47740,14 +47740,16 @@
         <v>0</v>
       </c>
       <c r="F751" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G751" s="7" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="G751" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B752" s="5" t="inlineStr">
@@ -47762,23 +47764,19 @@
       </c>
       <c r="D752" s="6" t="inlineStr">
         <is>
-          <t>ABNQ34GM3T</t>
-        </is>
-      </c>
-      <c r="E752" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F752" s="7" t="n">
-        <v>6</v>
-      </c>
+          <t>ABNQ55GM3T</t>
+        </is>
+      </c>
+      <c r="E752" s="7" t="n"/>
+      <c r="F752" s="7" t="n"/>
       <c r="G752" s="7" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B753" s="5" t="inlineStr">
@@ -47805,7 +47803,7 @@
     <row r="754">
       <c r="A754" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B754" s="5" t="inlineStr">
@@ -47832,7 +47830,7 @@
     <row r="755">
       <c r="A755" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B755" s="5" t="inlineStr">
@@ -47853,13 +47851,13 @@
       <c r="E755" s="7" t="n"/>
       <c r="F755" s="7" t="n"/>
       <c r="G755" s="7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B756" s="5" t="inlineStr">
@@ -47886,12 +47884,12 @@
     <row r="757">
       <c r="A757" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B757" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C757" s="6" t="inlineStr">
@@ -47904,10 +47902,12 @@
           <t>ABNQ55GM3T</t>
         </is>
       </c>
-      <c r="E757" s="7" t="n"/>
+      <c r="E757" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F757" s="7" t="n"/>
       <c r="G757" s="7" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="758">
@@ -47918,7 +47918,7 @@
       </c>
       <c r="B758" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C758" s="6" t="inlineStr">
@@ -47934,15 +47934,17 @@
       <c r="E758" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F758" s="7" t="n"/>
+      <c r="F758" s="7" t="n">
+        <v>14</v>
+      </c>
       <c r="G758" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B759" s="5" t="inlineStr">
@@ -47957,23 +47959,19 @@
       </c>
       <c r="D759" s="6" t="inlineStr">
         <is>
-          <t>ABNQ55GM3T</t>
-        </is>
-      </c>
-      <c r="E759" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F759" s="7" t="n">
-        <v>14</v>
-      </c>
+          <t>ABNW55GM3T</t>
+        </is>
+      </c>
+      <c r="E759" s="7" t="n"/>
+      <c r="F759" s="7" t="n"/>
       <c r="G759" s="7" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B760" s="5" t="inlineStr">
@@ -48000,7 +47998,7 @@
     <row r="761">
       <c r="A761" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B761" s="5" t="inlineStr">
@@ -48021,13 +48019,13 @@
       <c r="E761" s="7" t="n"/>
       <c r="F761" s="7" t="n"/>
       <c r="G761" s="7" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B762" s="5" t="inlineStr">
@@ -48054,7 +48052,7 @@
     <row r="763">
       <c r="A763" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B763" s="5" t="inlineStr">
@@ -48081,7 +48079,7 @@
     <row r="764">
       <c r="A764" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B764" s="5" t="inlineStr">
@@ -48099,8 +48097,12 @@
           <t>ABNW55GM3T</t>
         </is>
       </c>
-      <c r="E764" s="7" t="n"/>
-      <c r="F764" s="7" t="n"/>
+      <c r="E764" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F764" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="G764" s="7" t="n">
         <v>1</v>
       </c>
@@ -48108,7 +48110,7 @@
     <row r="765">
       <c r="A765" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B765" s="5" t="inlineStr">
@@ -48118,28 +48120,24 @@
       </c>
       <c r="C765" s="6" t="inlineStr">
         <is>
-          <t>Concealed Set</t>
+          <t>Floor Standing AC</t>
         </is>
       </c>
       <c r="D765" s="6" t="inlineStr">
         <is>
-          <t>ABNW55GM3T</t>
-        </is>
-      </c>
-      <c r="E765" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F765" s="7" t="n">
-        <v>1</v>
-      </c>
+          <t>APNQ55GT3M6-AUUQ55GT</t>
+        </is>
+      </c>
+      <c r="E765" s="7" t="n"/>
+      <c r="F765" s="7" t="n"/>
       <c r="G765" s="7" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B766" s="5" t="inlineStr">
@@ -48166,7 +48164,7 @@
     <row r="767">
       <c r="A767" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B767" s="5" t="inlineStr">
@@ -48193,7 +48191,7 @@
     <row r="768">
       <c r="A768" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B768" s="5" t="inlineStr">
@@ -48220,7 +48218,7 @@
     <row r="769">
       <c r="A769" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B769" s="5" t="inlineStr">
@@ -48247,7 +48245,7 @@
     <row r="770">
       <c r="A770" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B770" s="5" t="inlineStr">
@@ -48257,24 +48255,24 @@
       </c>
       <c r="C770" s="6" t="inlineStr">
         <is>
-          <t>Floor Standing AC</t>
+          <t>Cassette AC</t>
         </is>
       </c>
       <c r="D770" s="6" t="inlineStr">
         <is>
-          <t>APNQ55GT3M6-AUUQ55GT</t>
+          <t>ATNQ36GNL</t>
         </is>
       </c>
       <c r="E770" s="7" t="n"/>
       <c r="F770" s="7" t="n"/>
       <c r="G770" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B771" s="5" t="inlineStr">
@@ -48301,7 +48299,7 @@
     <row r="772">
       <c r="A772" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B772" s="5" t="inlineStr">
@@ -48328,7 +48326,7 @@
     <row r="773">
       <c r="A773" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B773" s="5" t="inlineStr">
@@ -48355,7 +48353,7 @@
     <row r="774">
       <c r="A774" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B774" s="5" t="inlineStr">
@@ -48382,7 +48380,7 @@
     <row r="775">
       <c r="A775" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B775" s="5" t="inlineStr">
@@ -48400,7 +48398,9 @@
           <t>ATNQ36GNL</t>
         </is>
       </c>
-      <c r="E775" s="7" t="n"/>
+      <c r="E775" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F775" s="7" t="n"/>
       <c r="G775" s="7" t="n">
         <v>1</v>
@@ -48409,7 +48409,7 @@
     <row r="776">
       <c r="A776" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B776" s="5" t="inlineStr">
@@ -48419,26 +48419,24 @@
       </c>
       <c r="C776" s="6" t="inlineStr">
         <is>
-          <t>Cassette AC</t>
+          <t>Concealed Set</t>
         </is>
       </c>
       <c r="D776" s="6" t="inlineStr">
         <is>
-          <t>ATNQ36GNL</t>
-        </is>
-      </c>
-      <c r="E776" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ABNQ60LM3T</t>
+        </is>
+      </c>
+      <c r="E776" s="7" t="n"/>
       <c r="F776" s="7" t="n"/>
       <c r="G776" s="7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B777" s="5" t="inlineStr">
@@ -48457,7 +48455,9 @@
         </is>
       </c>
       <c r="E777" s="7" t="n"/>
-      <c r="F777" s="7" t="n"/>
+      <c r="F777" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="G777" s="7" t="n">
         <v>16</v>
       </c>
@@ -48465,7 +48465,7 @@
     <row r="778">
       <c r="A778" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B778" s="5" t="inlineStr">
@@ -48484,9 +48484,7 @@
         </is>
       </c>
       <c r="E778" s="7" t="n"/>
-      <c r="F778" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="F778" s="7" t="n"/>
       <c r="G778" s="7" t="n">
         <v>16</v>
       </c>
@@ -48494,7 +48492,7 @@
     <row r="779">
       <c r="A779" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B779" s="5" t="inlineStr">
@@ -48521,7 +48519,7 @@
     <row r="780">
       <c r="A780" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B780" s="5" t="inlineStr">
@@ -48548,7 +48546,7 @@
     <row r="781">
       <c r="A781" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B781" s="5" t="inlineStr">
@@ -48566,16 +48564,20 @@
           <t>ABNQ60LM3T</t>
         </is>
       </c>
-      <c r="E781" s="7" t="n"/>
-      <c r="F781" s="7" t="n"/>
+      <c r="E781" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F781" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G781" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B782" s="5" t="inlineStr">
@@ -48590,23 +48592,19 @@
       </c>
       <c r="D782" s="6" t="inlineStr">
         <is>
-          <t>ABNQ60LM3T</t>
-        </is>
-      </c>
-      <c r="E782" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F782" s="7" t="n">
-        <v>2</v>
-      </c>
+          <t>ABNW21GM1T</t>
+        </is>
+      </c>
+      <c r="E782" s="7" t="n"/>
+      <c r="F782" s="7" t="n"/>
       <c r="G782" s="7" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B783" s="5" t="inlineStr">
@@ -48633,7 +48631,7 @@
     <row r="784">
       <c r="A784" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B784" s="5" t="inlineStr">
@@ -48654,13 +48652,13 @@
       <c r="E784" s="7" t="n"/>
       <c r="F784" s="7" t="n"/>
       <c r="G784" s="7" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B785" s="5" t="inlineStr">
@@ -48687,7 +48685,7 @@
     <row r="786">
       <c r="A786" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B786" s="5" t="inlineStr">
@@ -48714,7 +48712,7 @@
     <row r="787">
       <c r="A787" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B787" s="5" t="inlineStr">
@@ -48732,16 +48730,18 @@
           <t>ABNW21GM1T</t>
         </is>
       </c>
-      <c r="E787" s="7" t="n"/>
+      <c r="E787" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F787" s="7" t="n"/>
       <c r="G787" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B788" s="5" t="inlineStr">
@@ -48751,26 +48751,24 @@
       </c>
       <c r="C788" s="6" t="inlineStr">
         <is>
-          <t>Concealed Set</t>
+          <t>Cassette AC</t>
         </is>
       </c>
       <c r="D788" s="6" t="inlineStr">
         <is>
-          <t>ABNW21GM1T</t>
-        </is>
-      </c>
-      <c r="E788" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ATNQ34GNL</t>
+        </is>
+      </c>
+      <c r="E788" s="7" t="n"/>
       <c r="F788" s="7" t="n"/>
       <c r="G788" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B789" s="5" t="inlineStr">
@@ -48789,15 +48787,17 @@
         </is>
       </c>
       <c r="E789" s="7" t="n"/>
-      <c r="F789" s="7" t="n"/>
+      <c r="F789" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="G789" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B790" s="5" t="inlineStr">
@@ -48816,9 +48816,7 @@
         </is>
       </c>
       <c r="E790" s="7" t="n"/>
-      <c r="F790" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="F790" s="7" t="n"/>
       <c r="G790" s="7" t="n">
         <v>5</v>
       </c>
@@ -48826,7 +48824,7 @@
     <row r="791">
       <c r="A791" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B791" s="5" t="inlineStr">
@@ -48853,7 +48851,7 @@
     <row r="792">
       <c r="A792" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B792" s="5" t="inlineStr">
@@ -48880,12 +48878,12 @@
     <row r="793">
       <c r="A793" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B793" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C793" s="6" t="inlineStr">
@@ -48898,11 +48896,13 @@
           <t>ATNQ34GNL</t>
         </is>
       </c>
-      <c r="E793" s="7" t="n"/>
-      <c r="F793" s="7" t="n"/>
-      <c r="G793" s="7" t="n">
-        <v>5</v>
-      </c>
+      <c r="E793" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F793" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G793" s="7" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="5" t="inlineStr">
@@ -48912,7 +48912,7 @@
       </c>
       <c r="B794" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C794" s="6" t="inlineStr">
@@ -48928,15 +48928,15 @@
       <c r="E794" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F794" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="G794" s="7" t="n"/>
+      <c r="F794" s="7" t="n"/>
+      <c r="G794" s="7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B795" s="5" t="inlineStr">
@@ -48946,26 +48946,24 @@
       </c>
       <c r="C795" s="6" t="inlineStr">
         <is>
-          <t>Cassette AC</t>
+          <t>Concealed Set</t>
         </is>
       </c>
       <c r="D795" s="6" t="inlineStr">
         <is>
-          <t>ATNQ34GNL</t>
-        </is>
-      </c>
-      <c r="E795" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ABNQ28GM1T</t>
+        </is>
+      </c>
+      <c r="E795" s="7" t="n"/>
       <c r="F795" s="7" t="n"/>
       <c r="G795" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B796" s="5" t="inlineStr">
@@ -48986,13 +48984,13 @@
       <c r="E796" s="7" t="n"/>
       <c r="F796" s="7" t="n"/>
       <c r="G796" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B797" s="5" t="inlineStr">
@@ -49019,7 +49017,7 @@
     <row r="798">
       <c r="A798" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B798" s="5" t="inlineStr">
@@ -49046,7 +49044,7 @@
     <row r="799">
       <c r="A799" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B799" s="5" t="inlineStr">
@@ -49064,16 +49062,18 @@
           <t>ABNQ28GM1T</t>
         </is>
       </c>
-      <c r="E799" s="7" t="n"/>
+      <c r="E799" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F799" s="7" t="n"/>
       <c r="G799" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B800" s="5" t="inlineStr">
@@ -49083,26 +49083,24 @@
       </c>
       <c r="C800" s="6" t="inlineStr">
         <is>
-          <t>Concealed Set</t>
+          <t>Cassette AC</t>
         </is>
       </c>
       <c r="D800" s="6" t="inlineStr">
         <is>
-          <t>ABNQ28GM1T</t>
-        </is>
-      </c>
-      <c r="E800" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ATNQ55GML</t>
+        </is>
+      </c>
+      <c r="E800" s="7" t="n"/>
       <c r="F800" s="7" t="n"/>
       <c r="G800" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B801" s="5" t="inlineStr">
@@ -49129,7 +49127,7 @@
     <row r="802">
       <c r="A802" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B802" s="5" t="inlineStr">
@@ -49156,7 +49154,7 @@
     <row r="803">
       <c r="A803" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B803" s="5" t="inlineStr">
@@ -49183,7 +49181,7 @@
     <row r="804">
       <c r="A804" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B804" s="5" t="inlineStr">
@@ -49210,7 +49208,7 @@
     <row r="805">
       <c r="A805" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B805" s="5" t="inlineStr">
@@ -49228,16 +49226,18 @@
           <t>ATNQ55GML</t>
         </is>
       </c>
-      <c r="E805" s="7" t="n"/>
-      <c r="F805" s="7" t="n"/>
-      <c r="G805" s="7" t="n">
+      <c r="E805" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F805" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="G805" s="7" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B806" s="5" t="inlineStr">
@@ -49247,31 +49247,29 @@
       </c>
       <c r="C806" s="6" t="inlineStr">
         <is>
-          <t>Cassette AC</t>
+          <t>Split AC (Inverter)</t>
         </is>
       </c>
       <c r="D806" s="6" t="inlineStr">
         <is>
-          <t>ATNQ55GML</t>
-        </is>
-      </c>
-      <c r="E806" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F806" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G806" s="7" t="n"/>
+          <t>NF182C</t>
+        </is>
+      </c>
+      <c r="E806" s="7" t="n"/>
+      <c r="F806" s="7" t="n"/>
+      <c r="G806" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B807" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>eXtra</t>
         </is>
       </c>
       <c r="C807" s="6" t="inlineStr">
@@ -49285,10 +49283,10 @@
         </is>
       </c>
       <c r="E807" s="7" t="n"/>
-      <c r="F807" s="7" t="n"/>
-      <c r="G807" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="F807" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G807" s="7" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="5" t="inlineStr">
@@ -49298,7 +49296,7 @@
       </c>
       <c r="B808" s="5" t="inlineStr">
         <is>
-          <t>eXtra</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C808" s="6" t="inlineStr">
@@ -49312,15 +49310,15 @@
         </is>
       </c>
       <c r="E808" s="7" t="n"/>
-      <c r="F808" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G808" s="7" t="n"/>
+      <c r="F808" s="7" t="n"/>
+      <c r="G808" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="809">
       <c r="A809" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B809" s="5" t="inlineStr">
@@ -49347,12 +49345,12 @@
     <row r="810">
       <c r="A810" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C810" s="6" t="inlineStr">
@@ -49366,10 +49364,10 @@
         </is>
       </c>
       <c r="E810" s="7" t="n"/>
-      <c r="F810" s="7" t="n"/>
-      <c r="G810" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="F810" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G810" s="7" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="5" t="inlineStr">
@@ -49379,7 +49377,7 @@
       </c>
       <c r="B811" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C811" s="6" t="inlineStr">
@@ -49393,15 +49391,15 @@
         </is>
       </c>
       <c r="E811" s="7" t="n"/>
-      <c r="F811" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G811" s="7" t="n"/>
+      <c r="F811" s="7" t="n"/>
+      <c r="G811" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B812" s="5" t="inlineStr">
@@ -49428,12 +49426,12 @@
     <row r="813">
       <c r="A813" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B813" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C813" s="6" t="inlineStr">
@@ -49446,10 +49444,14 @@
           <t>NF182C</t>
         </is>
       </c>
-      <c r="E813" s="7" t="n"/>
-      <c r="F813" s="7" t="n"/>
+      <c r="E813" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F813" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="G813" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="814">
@@ -49460,7 +49462,7 @@
       </c>
       <c r="B814" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C814" s="6" t="inlineStr">
@@ -49476,17 +49478,15 @@
       <c r="E814" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F814" s="7" t="n">
+      <c r="F814" s="7" t="n"/>
+      <c r="G814" s="7" t="n">
         <v>1</v>
-      </c>
-      <c r="G814" s="7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B815" s="5" t="inlineStr">
@@ -49496,26 +49496,24 @@
       </c>
       <c r="C815" s="6" t="inlineStr">
         <is>
-          <t>Split AC (Inverter)</t>
+          <t>Concealed Set</t>
         </is>
       </c>
       <c r="D815" s="6" t="inlineStr">
         <is>
-          <t>NF182C</t>
-        </is>
-      </c>
-      <c r="E815" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ABNW28GM1T</t>
+        </is>
+      </c>
+      <c r="E815" s="7" t="n"/>
       <c r="F815" s="7" t="n"/>
       <c r="G815" s="7" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B816" s="5" t="inlineStr">
@@ -49542,7 +49540,7 @@
     <row r="817">
       <c r="A817" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B817" s="5" t="inlineStr">
@@ -49561,15 +49559,15 @@
         </is>
       </c>
       <c r="E817" s="7" t="n"/>
-      <c r="F817" s="7" t="n"/>
-      <c r="G817" s="7" t="n">
-        <v>31</v>
-      </c>
+      <c r="F817" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G817" s="7" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B818" s="5" t="inlineStr">
@@ -49584,19 +49582,19 @@
       </c>
       <c r="D818" s="6" t="inlineStr">
         <is>
-          <t>ABNW28GM1T</t>
+          <t>ABNQ40GM3T</t>
         </is>
       </c>
       <c r="E818" s="7" t="n"/>
-      <c r="F818" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G818" s="7" t="n"/>
+      <c r="F818" s="7" t="n"/>
+      <c r="G818" s="7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B819" s="5" t="inlineStr">
@@ -49623,12 +49621,12 @@
     <row r="820">
       <c r="A820" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B820" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C820" s="6" t="inlineStr">
@@ -49641,11 +49639,13 @@
           <t>ABNQ40GM3T</t>
         </is>
       </c>
-      <c r="E820" s="7" t="n"/>
-      <c r="F820" s="7" t="n"/>
-      <c r="G820" s="7" t="n">
-        <v>20</v>
-      </c>
+      <c r="E820" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F820" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G820" s="7" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="5" t="inlineStr">
@@ -49655,7 +49655,7 @@
       </c>
       <c r="B821" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C821" s="6" t="inlineStr">
@@ -49669,17 +49669,17 @@
         </is>
       </c>
       <c r="E821" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F821" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G821" s="7" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F821" s="7" t="n"/>
+      <c r="G821" s="7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="B822" s="5" t="inlineStr">
@@ -49689,26 +49689,24 @@
       </c>
       <c r="C822" s="6" t="inlineStr">
         <is>
-          <t>Concealed Set</t>
+          <t>Cassette AC</t>
         </is>
       </c>
       <c r="D822" s="6" t="inlineStr">
         <is>
-          <t>ABNQ40GM3T</t>
-        </is>
-      </c>
-      <c r="E822" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ATNW40GYL</t>
+        </is>
+      </c>
+      <c r="E822" s="7" t="n"/>
       <c r="F822" s="7" t="n"/>
       <c r="G822" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" s="5" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B823" s="5" t="inlineStr">
@@ -49729,13 +49727,13 @@
       <c r="E823" s="7" t="n"/>
       <c r="F823" s="7" t="n"/>
       <c r="G823" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B824" s="5" t="inlineStr">
@@ -49762,7 +49760,7 @@
     <row r="825">
       <c r="A825" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B825" s="5" t="inlineStr">
@@ -49789,7 +49787,7 @@
     <row r="826">
       <c r="A826" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B826" s="5" t="inlineStr">
@@ -49808,15 +49806,17 @@
         </is>
       </c>
       <c r="E826" s="7" t="n"/>
-      <c r="F826" s="7" t="n"/>
+      <c r="F826" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="G826" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B827" s="5" t="inlineStr">
@@ -49834,7 +49834,9 @@
           <t>ATNW40GYL</t>
         </is>
       </c>
-      <c r="E827" s="7" t="n"/>
+      <c r="E827" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F827" s="7" t="n">
         <v>1</v>
       </c>
@@ -49845,38 +49847,34 @@
     <row r="828">
       <c r="A828" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B828" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>eXtra</t>
         </is>
       </c>
       <c r="C828" s="6" t="inlineStr">
         <is>
-          <t>Cassette AC</t>
+          <t>Window AC</t>
         </is>
       </c>
       <c r="D828" s="6" t="inlineStr">
         <is>
-          <t>ATNW40GYL</t>
-        </is>
-      </c>
-      <c r="E828" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>C182E</t>
+        </is>
+      </c>
+      <c r="E828" s="7" t="n"/>
       <c r="F828" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G828" s="7" t="n">
-        <v>4</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="G828" s="7" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B829" s="5" t="inlineStr">
@@ -49896,14 +49894,14 @@
       </c>
       <c r="E829" s="7" t="n"/>
       <c r="F829" s="7" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G829" s="7" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B830" s="5" t="inlineStr">
@@ -49923,14 +49921,14 @@
       </c>
       <c r="E830" s="7" t="n"/>
       <c r="F830" s="7" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="G830" s="7" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B831" s="5" t="inlineStr">
@@ -49950,14 +49948,14 @@
       </c>
       <c r="E831" s="7" t="n"/>
       <c r="F831" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G831" s="7" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B832" s="5" t="inlineStr">
@@ -49975,7 +49973,9 @@
           <t>C182E</t>
         </is>
       </c>
-      <c r="E832" s="7" t="n"/>
+      <c r="E832" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F832" s="7" t="n">
         <v>1</v>
       </c>
@@ -49984,31 +49984,31 @@
     <row r="833">
       <c r="A833" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B833" s="5" t="inlineStr">
         <is>
-          <t>eXtra</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C833" s="6" t="inlineStr">
         <is>
-          <t>Window AC</t>
+          <t>Split AC (On/Off)</t>
         </is>
       </c>
       <c r="D833" s="6" t="inlineStr">
         <is>
-          <t>C182E</t>
-        </is>
-      </c>
-      <c r="E833" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>LK242C</t>
+        </is>
+      </c>
+      <c r="E833" s="7" t="n"/>
       <c r="F833" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G833" s="7" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="G833" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="834">
       <c r="A834" s="5" t="inlineStr">
@@ -50018,7 +50018,7 @@
       </c>
       <c r="B834" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C834" s="6" t="inlineStr">
@@ -50033,21 +50033,21 @@
       </c>
       <c r="E834" s="7" t="n"/>
       <c r="F834" s="7" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G834" s="7" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B835" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C835" s="6" t="inlineStr">
@@ -50062,11 +50062,9 @@
       </c>
       <c r="E835" s="7" t="n"/>
       <c r="F835" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="G835" s="7" t="n">
-        <v>62</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G835" s="7" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="5" t="inlineStr">
@@ -50076,7 +50074,7 @@
       </c>
       <c r="B836" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C836" s="6" t="inlineStr">
@@ -50091,9 +50089,11 @@
       </c>
       <c r="E836" s="7" t="n"/>
       <c r="F836" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="G836" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="G836" s="7" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837" s="5" t="inlineStr">
@@ -50103,7 +50103,7 @@
       </c>
       <c r="B837" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C837" s="6" t="inlineStr">
@@ -50118,21 +50118,21 @@
       </c>
       <c r="E837" s="7" t="n"/>
       <c r="F837" s="7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G837" s="7" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B838" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C838" s="6" t="inlineStr">
@@ -50147,11 +50147,9 @@
       </c>
       <c r="E838" s="7" t="n"/>
       <c r="F838" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="G838" s="7" t="n">
-        <v>41</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="G838" s="7" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="5" t="inlineStr">
@@ -50161,7 +50159,7 @@
       </c>
       <c r="B839" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C839" s="6" t="inlineStr">
@@ -50176,7 +50174,7 @@
       </c>
       <c r="E839" s="7" t="n"/>
       <c r="F839" s="7" t="n">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="G839" s="7" t="n"/>
     </row>
@@ -50188,7 +50186,7 @@
       </c>
       <c r="B840" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C840" s="6" t="inlineStr">
@@ -50203,19 +50201,21 @@
       </c>
       <c r="E840" s="7" t="n"/>
       <c r="F840" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="G840" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="G840" s="7" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B841" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C841" s="6" t="inlineStr">
@@ -50230,11 +50230,9 @@
       </c>
       <c r="E841" s="7" t="n"/>
       <c r="F841" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="G841" s="7" t="n">
-        <v>23</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="G841" s="7" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="5" t="inlineStr">
@@ -50244,7 +50242,7 @@
       </c>
       <c r="B842" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C842" s="6" t="inlineStr">
@@ -50259,9 +50257,11 @@
       </c>
       <c r="E842" s="7" t="n"/>
       <c r="F842" s="7" t="n">
-        <v>236</v>
-      </c>
-      <c r="G842" s="7" t="n"/>
+        <v>78</v>
+      </c>
+      <c r="G842" s="7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843" s="5" t="inlineStr">
@@ -50271,7 +50271,7 @@
       </c>
       <c r="B843" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C843" s="6" t="inlineStr">
@@ -50286,21 +50286,21 @@
       </c>
       <c r="E843" s="7" t="n"/>
       <c r="F843" s="7" t="n">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="G843" s="7" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B844" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C844" s="6" t="inlineStr">
@@ -50313,12 +50313,14 @@
           <t>LK242C</t>
         </is>
       </c>
-      <c r="E844" s="7" t="n"/>
+      <c r="E844" s="7" t="n">
+        <v>725</v>
+      </c>
       <c r="F844" s="7" t="n">
-        <v>116</v>
+        <v>639</v>
       </c>
       <c r="G844" s="7" t="n">
-        <v>57</v>
+        <v>152</v>
       </c>
     </row>
     <row r="845">
@@ -50329,7 +50331,7 @@
       </c>
       <c r="B845" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C845" s="6" t="inlineStr">
@@ -50343,13 +50345,13 @@
         </is>
       </c>
       <c r="E845" s="7" t="n">
-        <v>725</v>
+        <v>80</v>
       </c>
       <c r="F845" s="7" t="n">
-        <v>639</v>
+        <v>171</v>
       </c>
       <c r="G845" s="7" t="n">
-        <v>152</v>
+        <v>14</v>
       </c>
     </row>
     <row r="846">
@@ -50360,7 +50362,7 @@
       </c>
       <c r="B846" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C846" s="6" t="inlineStr">
@@ -50374,24 +50376,24 @@
         </is>
       </c>
       <c r="E846" s="7" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F846" s="7" t="n">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="G846" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B847" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C847" s="6" t="inlineStr">
@@ -50401,17 +50403,15 @@
       </c>
       <c r="D847" s="6" t="inlineStr">
         <is>
-          <t>LK242C</t>
-        </is>
-      </c>
-      <c r="E847" s="7" t="n">
-        <v>150</v>
-      </c>
+          <t>LK242H</t>
+        </is>
+      </c>
+      <c r="E847" s="7" t="n"/>
       <c r="F847" s="7" t="n">
-        <v>190</v>
+        <v>3</v>
       </c>
       <c r="G847" s="7" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="848">
@@ -50422,7 +50422,7 @@
       </c>
       <c r="B848" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C848" s="6" t="inlineStr">
@@ -50437,21 +50437,21 @@
       </c>
       <c r="E848" s="7" t="n"/>
       <c r="F848" s="7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G848" s="7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B849" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C849" s="6" t="inlineStr">
@@ -50466,11 +50466,9 @@
       </c>
       <c r="E849" s="7" t="n"/>
       <c r="F849" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="G849" s="7" t="n">
-        <v>11</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G849" s="7" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="5" t="inlineStr">
@@ -50480,7 +50478,7 @@
       </c>
       <c r="B850" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C850" s="6" t="inlineStr">
@@ -50495,9 +50493,11 @@
       </c>
       <c r="E850" s="7" t="n"/>
       <c r="F850" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G850" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G850" s="7" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="5" t="inlineStr">
@@ -50507,7 +50507,7 @@
       </c>
       <c r="B851" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C851" s="6" t="inlineStr">
@@ -50522,21 +50522,21 @@
       </c>
       <c r="E851" s="7" t="n"/>
       <c r="F851" s="7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G851" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B852" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C852" s="6" t="inlineStr">
@@ -50551,11 +50551,9 @@
       </c>
       <c r="E852" s="7" t="n"/>
       <c r="F852" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G852" s="7" t="n">
-        <v>13</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G852" s="7" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="5" t="inlineStr">
@@ -50565,7 +50563,7 @@
       </c>
       <c r="B853" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C853" s="6" t="inlineStr">
@@ -50580,9 +50578,11 @@
       </c>
       <c r="E853" s="7" t="n"/>
       <c r="F853" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G853" s="7" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="G853" s="7" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" s="5" t="inlineStr">
@@ -50592,7 +50592,7 @@
       </c>
       <c r="B854" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C854" s="6" t="inlineStr">
@@ -50607,7 +50607,7 @@
       </c>
       <c r="E854" s="7" t="n"/>
       <c r="F854" s="7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G854" s="7" t="n">
         <v>13</v>
@@ -50616,12 +50616,12 @@
     <row r="855">
       <c r="A855" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B855" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C855" s="6" t="inlineStr">
@@ -50636,11 +50636,9 @@
       </c>
       <c r="E855" s="7" t="n"/>
       <c r="F855" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="G855" s="7" t="n">
-        <v>13</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="G855" s="7" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="5" t="inlineStr">
@@ -50650,7 +50648,7 @@
       </c>
       <c r="B856" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C856" s="6" t="inlineStr">
@@ -50665,9 +50663,11 @@
       </c>
       <c r="E856" s="7" t="n"/>
       <c r="F856" s="7" t="n">
-        <v>117</v>
-      </c>
-      <c r="G856" s="7" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="G856" s="7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="857">
       <c r="A857" s="5" t="inlineStr">
@@ -50677,7 +50677,7 @@
       </c>
       <c r="B857" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C857" s="6" t="inlineStr">
@@ -50692,21 +50692,21 @@
       </c>
       <c r="E857" s="7" t="n"/>
       <c r="F857" s="7" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G857" s="7" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B858" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C858" s="6" t="inlineStr">
@@ -50719,12 +50719,14 @@
           <t>LK242H</t>
         </is>
       </c>
-      <c r="E858" s="7" t="n"/>
+      <c r="E858" s="7" t="n">
+        <v>165</v>
+      </c>
       <c r="F858" s="7" t="n">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="G858" s="7" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="859">
@@ -50735,7 +50737,7 @@
       </c>
       <c r="B859" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C859" s="6" t="inlineStr">
@@ -50749,13 +50751,13 @@
         </is>
       </c>
       <c r="E859" s="7" t="n">
-        <v>165</v>
+        <v>30</v>
       </c>
       <c r="F859" s="7" t="n">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="G859" s="7" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
     </row>
     <row r="860">
@@ -50766,7 +50768,7 @@
       </c>
       <c r="B860" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C860" s="6" t="inlineStr">
@@ -50780,24 +50782,24 @@
         </is>
       </c>
       <c r="E860" s="7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F860" s="7" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G860" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B861" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C861" s="6" t="inlineStr">
@@ -50807,17 +50809,15 @@
       </c>
       <c r="D861" s="6" t="inlineStr">
         <is>
-          <t>LK242H</t>
-        </is>
-      </c>
-      <c r="E861" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>LK182C</t>
+        </is>
+      </c>
+      <c r="E861" s="7" t="n"/>
       <c r="F861" s="7" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G861" s="7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="862">
@@ -50828,7 +50828,7 @@
       </c>
       <c r="B862" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C862" s="6" t="inlineStr">
@@ -50843,21 +50843,21 @@
       </c>
       <c r="E862" s="7" t="n"/>
       <c r="F862" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G862" s="7" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B863" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C863" s="6" t="inlineStr">
@@ -50872,11 +50872,9 @@
       </c>
       <c r="E863" s="7" t="n"/>
       <c r="F863" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G863" s="7" t="n">
-        <v>44</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G863" s="7" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="5" t="inlineStr">
@@ -50886,7 +50884,7 @@
       </c>
       <c r="B864" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C864" s="6" t="inlineStr">
@@ -50901,9 +50899,11 @@
       </c>
       <c r="E864" s="7" t="n"/>
       <c r="F864" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="G864" s="7" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="G864" s="7" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865" s="5" t="inlineStr">
@@ -50913,7 +50913,7 @@
       </c>
       <c r="B865" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C865" s="6" t="inlineStr">
@@ -50928,21 +50928,21 @@
       </c>
       <c r="E865" s="7" t="n"/>
       <c r="F865" s="7" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G865" s="7" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B866" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C866" s="6" t="inlineStr">
@@ -50957,11 +50957,9 @@
       </c>
       <c r="E866" s="7" t="n"/>
       <c r="F866" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G866" s="7" t="n">
-        <v>33</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G866" s="7" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="5" t="inlineStr">
@@ -50971,7 +50969,7 @@
       </c>
       <c r="B867" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C867" s="6" t="inlineStr">
@@ -50986,9 +50984,11 @@
       </c>
       <c r="E867" s="7" t="n"/>
       <c r="F867" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="G867" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="G867" s="7" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868" s="5" t="inlineStr">
@@ -50998,7 +50998,7 @@
       </c>
       <c r="B868" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C868" s="6" t="inlineStr">
@@ -51013,21 +51013,21 @@
       </c>
       <c r="E868" s="7" t="n"/>
       <c r="F868" s="7" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G868" s="7" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B869" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C869" s="6" t="inlineStr">
@@ -51042,11 +51042,9 @@
       </c>
       <c r="E869" s="7" t="n"/>
       <c r="F869" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G869" s="7" t="n">
-        <v>51</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="G869" s="7" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="5" t="inlineStr">
@@ -51056,7 +51054,7 @@
       </c>
       <c r="B870" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C870" s="6" t="inlineStr">
@@ -51071,9 +51069,11 @@
       </c>
       <c r="E870" s="7" t="n"/>
       <c r="F870" s="7" t="n">
-        <v>386</v>
-      </c>
-      <c r="G870" s="7" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="G870" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="871">
       <c r="A871" s="5" t="inlineStr">
@@ -51083,7 +51083,7 @@
       </c>
       <c r="B871" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C871" s="6" t="inlineStr">
@@ -51098,21 +51098,21 @@
       </c>
       <c r="E871" s="7" t="n"/>
       <c r="F871" s="7" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="G871" s="7" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B872" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C872" s="6" t="inlineStr">
@@ -51125,12 +51125,14 @@
           <t>LK182C</t>
         </is>
       </c>
-      <c r="E872" s="7" t="n"/>
+      <c r="E872" s="7" t="n">
+        <v>886</v>
+      </c>
       <c r="F872" s="7" t="n">
-        <v>95</v>
+        <v>668</v>
       </c>
       <c r="G872" s="7" t="n">
-        <v>81</v>
+        <v>301</v>
       </c>
     </row>
     <row r="873">
@@ -51141,7 +51143,7 @@
       </c>
       <c r="B873" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C873" s="6" t="inlineStr">
@@ -51155,13 +51157,13 @@
         </is>
       </c>
       <c r="E873" s="7" t="n">
-        <v>886</v>
+        <v>150</v>
       </c>
       <c r="F873" s="7" t="n">
-        <v>668</v>
+        <v>100</v>
       </c>
       <c r="G873" s="7" t="n">
-        <v>301</v>
+        <v>22</v>
       </c>
     </row>
     <row r="874">
@@ -51172,7 +51174,7 @@
       </c>
       <c r="B874" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C874" s="6" t="inlineStr">
@@ -51186,24 +51188,24 @@
         </is>
       </c>
       <c r="E874" s="7" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F874" s="7" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G874" s="7" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B875" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C875" s="6" t="inlineStr">
@@ -51213,17 +51215,15 @@
       </c>
       <c r="D875" s="6" t="inlineStr">
         <is>
-          <t>LK182C</t>
-        </is>
-      </c>
-      <c r="E875" s="7" t="n">
-        <v>100</v>
-      </c>
+          <t>LK182H</t>
+        </is>
+      </c>
+      <c r="E875" s="7" t="n"/>
       <c r="F875" s="7" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="G875" s="7" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="876">
@@ -51234,7 +51234,7 @@
       </c>
       <c r="B876" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C876" s="6" t="inlineStr">
@@ -51249,21 +51249,21 @@
       </c>
       <c r="E876" s="7" t="n"/>
       <c r="F876" s="7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G876" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B877" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C877" s="6" t="inlineStr">
@@ -51278,11 +51278,9 @@
       </c>
       <c r="E877" s="7" t="n"/>
       <c r="F877" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="G877" s="7" t="n">
-        <v>9</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G877" s="7" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="5" t="inlineStr">
@@ -51292,7 +51290,7 @@
       </c>
       <c r="B878" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C878" s="6" t="inlineStr">
@@ -51307,9 +51305,11 @@
       </c>
       <c r="E878" s="7" t="n"/>
       <c r="F878" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G878" s="7" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="G878" s="7" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="879">
       <c r="A879" s="5" t="inlineStr">
@@ -51319,7 +51319,7 @@
       </c>
       <c r="B879" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C879" s="6" t="inlineStr">
@@ -51334,21 +51334,21 @@
       </c>
       <c r="E879" s="7" t="n"/>
       <c r="F879" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G879" s="7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B880" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C880" s="6" t="inlineStr">
@@ -51363,11 +51363,9 @@
       </c>
       <c r="E880" s="7" t="n"/>
       <c r="F880" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G880" s="7" t="n">
-        <v>9</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G880" s="7" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="5" t="inlineStr">
@@ -51377,7 +51375,7 @@
       </c>
       <c r="B881" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C881" s="6" t="inlineStr">
@@ -51392,9 +51390,11 @@
       </c>
       <c r="E881" s="7" t="n"/>
       <c r="F881" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="G881" s="7" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="G881" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882" s="5" t="inlineStr">
@@ -51404,7 +51404,7 @@
       </c>
       <c r="B882" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C882" s="6" t="inlineStr">
@@ -51419,21 +51419,21 @@
       </c>
       <c r="E882" s="7" t="n"/>
       <c r="F882" s="7" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="G882" s="7" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B883" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C883" s="6" t="inlineStr">
@@ -51448,11 +51448,9 @@
       </c>
       <c r="E883" s="7" t="n"/>
       <c r="F883" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="G883" s="7" t="n">
-        <v>28</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="G883" s="7" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="5" t="inlineStr">
@@ -51462,7 +51460,7 @@
       </c>
       <c r="B884" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C884" s="6" t="inlineStr">
@@ -51477,9 +51475,11 @@
       </c>
       <c r="E884" s="7" t="n"/>
       <c r="F884" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="G884" s="7" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="G884" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885" s="5" t="inlineStr">
@@ -51489,7 +51489,7 @@
       </c>
       <c r="B885" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C885" s="6" t="inlineStr">
@@ -51504,21 +51504,21 @@
       </c>
       <c r="E885" s="7" t="n"/>
       <c r="F885" s="7" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G885" s="7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B886" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C886" s="6" t="inlineStr">
@@ -51531,12 +51531,14 @@
           <t>LK182H</t>
         </is>
       </c>
-      <c r="E886" s="7" t="n"/>
+      <c r="E886" s="7" t="n">
+        <v>60</v>
+      </c>
       <c r="F886" s="7" t="n">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="G886" s="7" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
     </row>
     <row r="887">
@@ -51547,7 +51549,7 @@
       </c>
       <c r="B887" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C887" s="6" t="inlineStr">
@@ -51561,13 +51563,13 @@
         </is>
       </c>
       <c r="E887" s="7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F887" s="7" t="n">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="G887" s="7" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="888">
@@ -51578,7 +51580,7 @@
       </c>
       <c r="B888" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C888" s="6" t="inlineStr">
@@ -51592,19 +51594,19 @@
         </is>
       </c>
       <c r="E888" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F888" s="7" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="G888" s="7" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B889" s="5" t="inlineStr">
@@ -51619,28 +51621,26 @@
       </c>
       <c r="D889" s="6" t="inlineStr">
         <is>
-          <t>LK182H</t>
-        </is>
-      </c>
-      <c r="E889" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>LT302C</t>
+        </is>
+      </c>
+      <c r="E889" s="7" t="n"/>
       <c r="F889" s="7" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G889" s="7" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B890" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C890" s="6" t="inlineStr">
@@ -51657,9 +51657,7 @@
       <c r="F890" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G890" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="G890" s="7" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="5" t="inlineStr">
@@ -51669,7 +51667,7 @@
       </c>
       <c r="B891" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C891" s="6" t="inlineStr">
@@ -51684,19 +51682,21 @@
       </c>
       <c r="E891" s="7" t="n"/>
       <c r="F891" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G891" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G891" s="7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B892" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C892" s="6" t="inlineStr">
@@ -51711,11 +51711,9 @@
       </c>
       <c r="E892" s="7" t="n"/>
       <c r="F892" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G892" s="7" t="n">
-        <v>7</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G892" s="7" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="5" t="inlineStr">
@@ -51725,7 +51723,7 @@
       </c>
       <c r="B893" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C893" s="6" t="inlineStr">
@@ -51740,9 +51738,11 @@
       </c>
       <c r="E893" s="7" t="n"/>
       <c r="F893" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="G893" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G893" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894" s="5" t="inlineStr">
@@ -51752,7 +51752,7 @@
       </c>
       <c r="B894" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C894" s="6" t="inlineStr">
@@ -51767,21 +51767,21 @@
       </c>
       <c r="E894" s="7" t="n"/>
       <c r="F894" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G894" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B895" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C895" s="6" t="inlineStr">
@@ -51796,11 +51796,9 @@
       </c>
       <c r="E895" s="7" t="n"/>
       <c r="F895" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G895" s="7" t="n">
-        <v>6</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G895" s="7" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="5" t="inlineStr">
@@ -51810,7 +51808,7 @@
       </c>
       <c r="B896" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C896" s="6" t="inlineStr">
@@ -51825,9 +51823,11 @@
       </c>
       <c r="E896" s="7" t="n"/>
       <c r="F896" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="G896" s="7" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="G896" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="897">
       <c r="A897" s="5" t="inlineStr">
@@ -51837,7 +51837,7 @@
       </c>
       <c r="B897" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C897" s="6" t="inlineStr">
@@ -51852,21 +51852,21 @@
       </c>
       <c r="E897" s="7" t="n"/>
       <c r="F897" s="7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G897" s="7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B898" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C898" s="6" t="inlineStr">
@@ -51879,12 +51879,14 @@
           <t>LT302C</t>
         </is>
       </c>
-      <c r="E898" s="7" t="n"/>
+      <c r="E898" s="7" t="n">
+        <v>80</v>
+      </c>
       <c r="F898" s="7" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="G898" s="7" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
     </row>
     <row r="899">
@@ -51895,7 +51897,7 @@
       </c>
       <c r="B899" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C899" s="6" t="inlineStr">
@@ -51909,13 +51911,13 @@
         </is>
       </c>
       <c r="E899" s="7" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="F899" s="7" t="n">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="G899" s="7" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="900">
@@ -51926,7 +51928,7 @@
       </c>
       <c r="B900" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C900" s="6" t="inlineStr">
@@ -51940,19 +51942,19 @@
         </is>
       </c>
       <c r="E900" s="7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F900" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G900" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B901" s="5" t="inlineStr">
@@ -51967,28 +51969,26 @@
       </c>
       <c r="D901" s="6" t="inlineStr">
         <is>
-          <t>LT302C</t>
-        </is>
-      </c>
-      <c r="E901" s="7" t="n">
-        <v>23</v>
-      </c>
+          <t>LT302H</t>
+        </is>
+      </c>
+      <c r="E901" s="7" t="n"/>
       <c r="F901" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G901" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="B902" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C902" s="6" t="inlineStr">
@@ -52005,9 +52005,7 @@
       <c r="F902" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G902" s="7" t="n">
-        <v>4</v>
-      </c>
+      <c r="G902" s="7" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="5" t="inlineStr">
@@ -52017,7 +52015,7 @@
       </c>
       <c r="B903" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C903" s="6" t="inlineStr">
@@ -52031,20 +52029,20 @@
         </is>
       </c>
       <c r="E903" s="7" t="n"/>
-      <c r="F903" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G903" s="7" t="n"/>
+      <c r="F903" s="7" t="n"/>
+      <c r="G903" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="904">
       <c r="A904" s="5" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B904" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C904" s="6" t="inlineStr">
@@ -52058,10 +52056,10 @@
         </is>
       </c>
       <c r="E904" s="7" t="n"/>
-      <c r="F904" s="7" t="n"/>
-      <c r="G904" s="7" t="n">
-        <v>4</v>
-      </c>
+      <c r="F904" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G904" s="7" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="5" t="inlineStr">
@@ -52071,7 +52069,7 @@
       </c>
       <c r="B905" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C905" s="6" t="inlineStr">
@@ -52088,7 +52086,9 @@
       <c r="F905" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G905" s="7" t="n"/>
+      <c r="G905" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" s="5" t="inlineStr">
@@ -52098,7 +52098,7 @@
       </c>
       <c r="B906" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C906" s="6" t="inlineStr">
@@ -52113,21 +52113,21 @@
       </c>
       <c r="E906" s="7" t="n"/>
       <c r="F906" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G906" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B907" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C907" s="6" t="inlineStr">
@@ -52142,11 +52142,9 @@
       </c>
       <c r="E907" s="7" t="n"/>
       <c r="F907" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G907" s="7" t="n">
-        <v>4</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G907" s="7" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="5" t="inlineStr">
@@ -52156,7 +52154,7 @@
       </c>
       <c r="B908" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C908" s="6" t="inlineStr">
@@ -52171,9 +52169,11 @@
       </c>
       <c r="E908" s="7" t="n"/>
       <c r="F908" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="G908" s="7" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="G908" s="7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909" s="5" t="inlineStr">
@@ -52183,7 +52183,7 @@
       </c>
       <c r="B909" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C909" s="6" t="inlineStr">
@@ -52198,21 +52198,21 @@
       </c>
       <c r="E909" s="7" t="n"/>
       <c r="F909" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G909" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B910" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C910" s="6" t="inlineStr">
@@ -52225,12 +52225,14 @@
           <t>LT302H</t>
         </is>
       </c>
-      <c r="E910" s="7" t="n"/>
+      <c r="E910" s="7" t="n">
+        <v>25</v>
+      </c>
       <c r="F910" s="7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G910" s="7" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="911">
@@ -52241,7 +52243,7 @@
       </c>
       <c r="B911" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C911" s="6" t="inlineStr">
@@ -52255,13 +52257,13 @@
         </is>
       </c>
       <c r="E911" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F911" s="7" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G911" s="7" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="912">
@@ -52272,7 +52274,7 @@
       </c>
       <c r="B912" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C912" s="6" t="inlineStr">
@@ -52286,72 +52288,70 @@
         </is>
       </c>
       <c r="E912" s="7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F912" s="7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G912" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Feb</t>
         </is>
       </c>
       <c r="B913" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C913" s="6" t="inlineStr">
         <is>
-          <t>Split AC (On/Off)</t>
+          <t>Cassette AC</t>
         </is>
       </c>
       <c r="D913" s="6" t="inlineStr">
         <is>
-          <t>LT302H</t>
-        </is>
-      </c>
-      <c r="E913" s="7" t="n">
-        <v>17</v>
-      </c>
+          <t>AUUQ34G</t>
+        </is>
+      </c>
+      <c r="E913" s="7" t="n"/>
       <c r="F913" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="G913" s="7" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G913" s="7" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="5" t="inlineStr">
         <is>
-          <t>Feb</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B914" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C914" s="6" t="inlineStr">
         <is>
-          <t>Cassette AC</t>
+          <t>Window AC</t>
         </is>
       </c>
       <c r="D914" s="6" t="inlineStr">
         <is>
-          <t>AUUQ34G</t>
+          <t>W242EC</t>
         </is>
       </c>
       <c r="E914" s="7" t="n"/>
       <c r="F914" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G914" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="G914" s="7" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915" s="5" t="inlineStr">
@@ -52361,7 +52361,7 @@
       </c>
       <c r="B915" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C915" s="6" t="inlineStr">
@@ -52375,22 +52375,20 @@
         </is>
       </c>
       <c r="E915" s="7" t="n"/>
-      <c r="F915" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="F915" s="7" t="n"/>
       <c r="G915" s="7" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B916" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C916" s="6" t="inlineStr">
@@ -52404,9 +52402,11 @@
         </is>
       </c>
       <c r="E916" s="7" t="n"/>
-      <c r="F916" s="7" t="n"/>
+      <c r="F916" s="7" t="n">
+        <v>23</v>
+      </c>
       <c r="G916" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="917">
@@ -52417,7 +52417,7 @@
       </c>
       <c r="B917" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C917" s="6" t="inlineStr">
@@ -52432,10 +52432,10 @@
       </c>
       <c r="E917" s="7" t="n"/>
       <c r="F917" s="7" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G917" s="7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="918">
@@ -52446,7 +52446,7 @@
       </c>
       <c r="B918" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C918" s="6" t="inlineStr">
@@ -52461,21 +52461,19 @@
       </c>
       <c r="E918" s="7" t="n"/>
       <c r="F918" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G918" s="7" t="n">
-        <v>17</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G918" s="7" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B919" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C919" s="6" t="inlineStr">
@@ -52488,11 +52486,15 @@
           <t>W242EC</t>
         </is>
       </c>
-      <c r="E919" s="7" t="n"/>
+      <c r="E919" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="F919" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="G919" s="7" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="G919" s="7" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="920">
       <c r="A920" s="5" t="inlineStr">
@@ -52502,7 +52504,7 @@
       </c>
       <c r="B920" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C920" s="6" t="inlineStr">
@@ -52516,13 +52518,13 @@
         </is>
       </c>
       <c r="E920" s="7" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="F920" s="7" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G920" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="921">
@@ -52533,7 +52535,7 @@
       </c>
       <c r="B921" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C921" s="6" t="inlineStr">
@@ -52547,24 +52549,24 @@
         </is>
       </c>
       <c r="E921" s="7" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="F921" s="7" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G921" s="7" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Apr</t>
         </is>
       </c>
       <c r="B922" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C922" s="6" t="inlineStr">
@@ -52574,17 +52576,15 @@
       </c>
       <c r="D922" s="6" t="inlineStr">
         <is>
-          <t>W242EC</t>
-        </is>
-      </c>
-      <c r="E922" s="7" t="n">
-        <v>130</v>
-      </c>
+          <t>W181EC</t>
+        </is>
+      </c>
+      <c r="E922" s="7" t="n"/>
       <c r="F922" s="7" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="G922" s="7" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="923">
@@ -52595,7 +52595,7 @@
       </c>
       <c r="B923" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C923" s="6" t="inlineStr">
@@ -52609,22 +52609,20 @@
         </is>
       </c>
       <c r="E923" s="7" t="n"/>
-      <c r="F923" s="7" t="n">
-        <v>6</v>
-      </c>
+      <c r="F923" s="7" t="n"/>
       <c r="G923" s="7" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" s="5" t="inlineStr">
         <is>
-          <t>Apr</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B924" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C924" s="6" t="inlineStr">
@@ -52638,9 +52636,11 @@
         </is>
       </c>
       <c r="E924" s="7" t="n"/>
-      <c r="F924" s="7" t="n"/>
+      <c r="F924" s="7" t="n">
+        <v>51</v>
+      </c>
       <c r="G924" s="7" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="925">
@@ -52651,7 +52651,7 @@
       </c>
       <c r="B925" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C925" s="6" t="inlineStr">
@@ -52666,10 +52666,10 @@
       </c>
       <c r="E925" s="7" t="n"/>
       <c r="F925" s="7" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="G925" s="7" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="926">
@@ -52680,7 +52680,7 @@
       </c>
       <c r="B926" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C926" s="6" t="inlineStr">
@@ -52695,21 +52695,21 @@
       </c>
       <c r="E926" s="7" t="n"/>
       <c r="F926" s="7" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G926" s="7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B927" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>SWS</t>
         </is>
       </c>
       <c r="C927" s="6" t="inlineStr">
@@ -52722,12 +52722,14 @@
           <t>W181EC</t>
         </is>
       </c>
-      <c r="E927" s="7" t="n"/>
+      <c r="E927" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="F927" s="7" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="G927" s="7" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="928">
@@ -52738,7 +52740,7 @@
       </c>
       <c r="B928" s="5" t="inlineStr">
         <is>
-          <t>SWS</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C928" s="6" t="inlineStr">
@@ -52752,13 +52754,13 @@
         </is>
       </c>
       <c r="E928" s="7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F928" s="7" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G928" s="7" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="929">
@@ -52769,7 +52771,7 @@
       </c>
       <c r="B929" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C929" s="6" t="inlineStr">
@@ -52783,45 +52785,41 @@
         </is>
       </c>
       <c r="E929" s="7" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F929" s="7" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G929" s="7" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B930" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C930" s="6" t="inlineStr">
         <is>
-          <t>Window AC</t>
+          <t>Concealed Set</t>
         </is>
       </c>
       <c r="D930" s="6" t="inlineStr">
         <is>
-          <t>W181EC</t>
-        </is>
-      </c>
-      <c r="E930" s="7" t="n">
-        <v>60</v>
-      </c>
+          <t>AUUQ21G</t>
+        </is>
+      </c>
+      <c r="E930" s="7" t="n"/>
       <c r="F930" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="G930" s="7" t="n">
-        <v>62</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G930" s="7" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="5" t="inlineStr">
@@ -52831,17 +52829,17 @@
       </c>
       <c r="B931" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C931" s="6" t="inlineStr">
         <is>
-          <t>Concealed Set</t>
+          <t>Cassette AC</t>
         </is>
       </c>
       <c r="D931" s="6" t="inlineStr">
         <is>
-          <t>AUUQ21G</t>
+          <t>ATNW28GPLT</t>
         </is>
       </c>
       <c r="E931" s="7" t="n"/>
@@ -52853,12 +52851,12 @@
     <row r="932">
       <c r="A932" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B932" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C932" s="6" t="inlineStr">
@@ -52871,10 +52869,10 @@
           <t>ATNW28GPLT</t>
         </is>
       </c>
-      <c r="E932" s="7" t="n"/>
-      <c r="F932" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="E932" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F932" s="7" t="n"/>
       <c r="G932" s="7" t="n"/>
     </row>
     <row r="933">
@@ -52885,7 +52883,7 @@
       </c>
       <c r="B933" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C933" s="6" t="inlineStr">
@@ -52899,15 +52897,17 @@
         </is>
       </c>
       <c r="E933" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F933" s="7" t="n"/>
-      <c r="G933" s="7" t="n"/>
+      <c r="G933" s="7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="934">
       <c r="A934" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B934" s="5" t="inlineStr">
@@ -52922,16 +52922,14 @@
       </c>
       <c r="D934" s="6" t="inlineStr">
         <is>
-          <t>ATNW28GPLT</t>
-        </is>
-      </c>
-      <c r="E934" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F934" s="7" t="n"/>
-      <c r="G934" s="7" t="n">
-        <v>7</v>
-      </c>
+          <t>ATUW28GPLT</t>
+        </is>
+      </c>
+      <c r="E934" s="7" t="n"/>
+      <c r="F934" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G934" s="7" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="5" t="inlineStr">
@@ -52951,7 +52949,7 @@
       </c>
       <c r="D935" s="6" t="inlineStr">
         <is>
-          <t>ATUW28GPLT</t>
+          <t>ATUW40GYLT</t>
         </is>
       </c>
       <c r="E935" s="7" t="n"/>
@@ -52963,7 +52961,7 @@
     <row r="936">
       <c r="A936" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B936" s="5" t="inlineStr">
@@ -52990,7 +52988,7 @@
     <row r="937">
       <c r="A937" s="5" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B937" s="5" t="inlineStr">
@@ -53005,12 +53003,12 @@
       </c>
       <c r="D937" s="6" t="inlineStr">
         <is>
-          <t>ATUW40GYLT</t>
+          <t>ATW21GPLTA</t>
         </is>
       </c>
       <c r="E937" s="7" t="n"/>
       <c r="F937" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G937" s="7" t="n"/>
     </row>
@@ -53032,12 +53030,12 @@
       </c>
       <c r="D938" s="6" t="inlineStr">
         <is>
-          <t>ATW21GPLTA</t>
+          <t>ATW28GPLTA</t>
         </is>
       </c>
       <c r="E938" s="7" t="n"/>
       <c r="F938" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G938" s="7" t="n"/>
     </row>
@@ -53059,24 +53057,24 @@
       </c>
       <c r="D939" s="6" t="inlineStr">
         <is>
-          <t>ATW28GPLTA</t>
+          <t>GTNW28GPLTA-ATUW28GPLTA</t>
         </is>
       </c>
       <c r="E939" s="7" t="n"/>
       <c r="F939" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G939" s="7" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B940" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C940" s="6" t="inlineStr">
@@ -53086,12 +53084,14 @@
       </c>
       <c r="D940" s="6" t="inlineStr">
         <is>
-          <t>GTNW28GPLTA-ATUW28GPLTA</t>
-        </is>
-      </c>
-      <c r="E940" s="7" t="n"/>
+          <t>ATNQ28GPL</t>
+        </is>
+      </c>
+      <c r="E940" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F940" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G940" s="7" t="n"/>
     </row>
@@ -53103,24 +53103,22 @@
       </c>
       <c r="B941" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C941" s="6" t="inlineStr">
         <is>
-          <t>Cassette AC</t>
+          <t>Concealed Set</t>
         </is>
       </c>
       <c r="D941" s="6" t="inlineStr">
         <is>
-          <t>ATNQ28GPL</t>
-        </is>
-      </c>
-      <c r="E941" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>ABQ40GM3TA</t>
+        </is>
+      </c>
+      <c r="E941" s="7" t="n"/>
       <c r="F941" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G941" s="7" t="n"/>
     </row>
@@ -53142,12 +53140,12 @@
       </c>
       <c r="D942" s="6" t="inlineStr">
         <is>
-          <t>ABQ40GM3TA</t>
+          <t>ABQ60GM3T</t>
         </is>
       </c>
       <c r="E942" s="7" t="n"/>
       <c r="F942" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G942" s="7" t="n"/>
     </row>
@@ -53159,23 +53157,23 @@
       </c>
       <c r="B943" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C943" s="6" t="inlineStr">
         <is>
-          <t>Concealed Set</t>
+          <t>Cassette AC</t>
         </is>
       </c>
       <c r="D943" s="6" t="inlineStr">
         <is>
-          <t>ABQ60GM3T</t>
-        </is>
-      </c>
-      <c r="E943" s="7" t="n"/>
-      <c r="F943" s="7" t="n">
-        <v>7</v>
-      </c>
+          <t>GTNQ34GNLT</t>
+        </is>
+      </c>
+      <c r="E943" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F943" s="7" t="n"/>
       <c r="G943" s="7" t="n"/>
     </row>
     <row r="944">
@@ -53186,7 +53184,7 @@
       </c>
       <c r="B944" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C944" s="6" t="inlineStr">
@@ -53200,10 +53198,12 @@
         </is>
       </c>
       <c r="E944" s="7" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F944" s="7" t="n"/>
-      <c r="G944" s="7" t="n"/>
+      <c r="G944" s="7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" s="5" t="inlineStr">
@@ -53223,15 +53223,15 @@
       </c>
       <c r="D945" s="6" t="inlineStr">
         <is>
-          <t>GTNQ34GNLT</t>
+          <t>GTNQ40GNLT</t>
         </is>
       </c>
       <c r="E945" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F945" s="7" t="n"/>
       <c r="G945" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="946">
@@ -53252,15 +53252,15 @@
       </c>
       <c r="D946" s="6" t="inlineStr">
         <is>
-          <t>GTNQ40GNLT</t>
+          <t>GTNQ55GMLT</t>
         </is>
       </c>
       <c r="E946" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F946" s="7" t="n"/>
       <c r="G946" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="947">
@@ -53271,7 +53271,7 @@
       </c>
       <c r="B947" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C947" s="6" t="inlineStr">
@@ -53281,16 +53281,14 @@
       </c>
       <c r="D947" s="6" t="inlineStr">
         <is>
-          <t>GTNQ55GMLT</t>
+          <t>GTNW21GPLT</t>
         </is>
       </c>
       <c r="E947" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F947" s="7" t="n"/>
-      <c r="G947" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="G947" s="7" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="5" t="inlineStr">
@@ -53300,7 +53298,7 @@
       </c>
       <c r="B948" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Khunizan</t>
         </is>
       </c>
       <c r="C948" s="6" t="inlineStr">
@@ -53314,10 +53312,12 @@
         </is>
       </c>
       <c r="E948" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F948" s="7" t="n"/>
-      <c r="G948" s="7" t="n"/>
+      <c r="G948" s="7" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="949">
       <c r="A949" s="5" t="inlineStr">
@@ -53337,15 +53337,15 @@
       </c>
       <c r="D949" s="6" t="inlineStr">
         <is>
-          <t>GTNW21GPLT</t>
+          <t>GTNW28GPLT</t>
         </is>
       </c>
       <c r="E949" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F949" s="7" t="n"/>
       <c r="G949" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="950">
@@ -53366,7 +53366,7 @@
       </c>
       <c r="D950" s="6" t="inlineStr">
         <is>
-          <t>GTNW28GPLT</t>
+          <t>GTNW40GNLT</t>
         </is>
       </c>
       <c r="E950" s="7" t="n">
@@ -53395,7 +53395,7 @@
       </c>
       <c r="D951" s="6" t="inlineStr">
         <is>
-          <t>GTNW40GNLT</t>
+          <t>GTNW55GMLT</t>
         </is>
       </c>
       <c r="E951" s="7" t="n">
@@ -53414,7 +53414,7 @@
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Al Khunizan</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C952" s="6" t="inlineStr">
@@ -53424,16 +53424,14 @@
       </c>
       <c r="D952" s="6" t="inlineStr">
         <is>
-          <t>GTNW55GMLT</t>
+          <t>GTNQ28GPLT</t>
         </is>
       </c>
       <c r="E952" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F952" s="7" t="n"/>
-      <c r="G952" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="G952" s="7" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="5" t="inlineStr">
@@ -53470,24 +53468,24 @@
       </c>
       <c r="B954" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C954" s="6" t="inlineStr">
         <is>
-          <t>Cassette AC</t>
+          <t>Split AC</t>
         </is>
       </c>
       <c r="D954" s="6" t="inlineStr">
         <is>
-          <t>GTNQ21GPLT</t>
-        </is>
-      </c>
-      <c r="E954" s="7" t="n">
-        <v>1</v>
-      </c>
+          <t>NF242H</t>
+        </is>
+      </c>
+      <c r="E954" s="7" t="n"/>
       <c r="F954" s="7" t="n"/>
-      <c r="G954" s="7" t="n"/>
+      <c r="G954" s="7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="955">
       <c r="A955" s="5" t="inlineStr">
@@ -53497,24 +53495,24 @@
       </c>
       <c r="B955" s="5" t="inlineStr">
         <is>
-          <t>Black Box</t>
+          <t>Al Manea</t>
         </is>
       </c>
       <c r="C955" s="6" t="inlineStr">
         <is>
-          <t>Cassette AC</t>
+          <t>Split AC</t>
         </is>
       </c>
       <c r="D955" s="6" t="inlineStr">
         <is>
-          <t>GTNQ28GPLT</t>
-        </is>
-      </c>
-      <c r="E955" s="7" t="n">
+          <t>NV242H</t>
+        </is>
+      </c>
+      <c r="E955" s="7" t="n"/>
+      <c r="F955" s="7" t="n"/>
+      <c r="G955" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F955" s="7" t="n"/>
-      <c r="G955" s="7" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="5" t="inlineStr">
@@ -53529,18 +53527,18 @@
       </c>
       <c r="C956" s="6" t="inlineStr">
         <is>
-          <t>Split AC</t>
+          <t>Window AC</t>
         </is>
       </c>
       <c r="D956" s="6" t="inlineStr">
         <is>
-          <t>NV242H</t>
+          <t>E182R</t>
         </is>
       </c>
       <c r="E956" s="7" t="n"/>
       <c r="F956" s="7" t="n"/>
       <c r="G956" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="957">
@@ -53578,24 +53576,24 @@
       </c>
       <c r="B958" s="5" t="inlineStr">
         <is>
-          <t>Al Manea</t>
+          <t>Black Box</t>
         </is>
       </c>
       <c r="C958" s="6" t="inlineStr">
         <is>
-          <t>Split AC</t>
+          <t>Cassette AC</t>
         </is>
       </c>
       <c r="D958" s="6" t="inlineStr">
         <is>
-          <t>NV182C</t>
-        </is>
-      </c>
-      <c r="E958" s="7" t="n"/>
+          <t>GTNQ21GPLT</t>
+        </is>
+      </c>
+      <c r="E958" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F958" s="7" t="n"/>
-      <c r="G958" s="7" t="n">
-        <v>4</v>
-      </c>
+      <c r="G958" s="7" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="5" t="inlineStr">
@@ -53615,13 +53613,67 @@
       </c>
       <c r="D959" s="6" t="inlineStr">
         <is>
-          <t>NF242H</t>
+          <t>NV182C</t>
         </is>
       </c>
       <c r="E959" s="7" t="n"/>
       <c r="F959" s="7" t="n"/>
       <c r="G959" s="7" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="5" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B960" s="5" t="inlineStr">
+        <is>
+          <t>Al Manea</t>
+        </is>
+      </c>
+      <c r="C960" s="6" t="inlineStr">
+        <is>
+          <t>Window AC</t>
+        </is>
+      </c>
+      <c r="D960" s="6" t="inlineStr">
+        <is>
+          <t>E182A</t>
+        </is>
+      </c>
+      <c r="E960" s="7" t="n"/>
+      <c r="F960" s="7" t="n"/>
+      <c r="G960" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="5" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B961" s="5" t="inlineStr">
+        <is>
+          <t>Al Manea</t>
+        </is>
+      </c>
+      <c r="C961" s="6" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="D961" s="6" t="inlineStr">
+        <is>
+          <t>B1824C</t>
+        </is>
+      </c>
+      <c r="E961" s="7" t="n"/>
+      <c r="F961" s="7" t="n"/>
+      <c r="G961" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -53764,7 +53816,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  RAW_Category 행수: 836  ·  RAW_Model_2026 행수: 958</t>
+          <t xml:space="preserve">  RAW_Category 행수: 836  ·  RAW_Model_2026 행수: 960</t>
         </is>
       </c>
     </row>
